--- a/static/bank_statement_template.xlsx
+++ b/static/bank_statement_template.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Balance</t>
+          <t>Balance (optional)</t>
         </is>
       </c>
     </row>
